--- a/src/nodes/LPC/compressor_blade_self_frequency.xlsx
+++ b/src/nodes/LPC/compressor_blade_self_frequency.xlsx
@@ -543,58 +543,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>151.5563401134811</v>
+        <v>170.30173760301921</v>
       </c>
       <c r="C3">
-        <v>949.85592364164006</v>
+        <v>1067.3398034524266</v>
       </c>
       <c r="D3">
-        <v>2659.8916352712254</v>
+        <v>2988.8829921812849</v>
       </c>
       <c r="E3">
-        <v>5216.2324348391</v>
+        <v>5861.4073599901367</v>
       </c>
       <c r="F3">
-        <v>8619.2679878409581</v>
+        <v>9685.35076854119</v>
       </c>
       <c r="G3">
-        <v>12872.385612157519</v>
+        <v>14464.519499514703</v>
       </c>
       <c r="H3">
-        <v>874.90723431514027</v>
+        <v>1049.2758825253632</v>
       </c>
       <c r="I3">
-        <v>2624.7217029454209</v>
+        <v>3147.8276475760895</v>
       </c>
       <c r="J3">
-        <v>4374.5361715757008</v>
+        <v>5246.3794126268149</v>
       </c>
       <c r="K3">
-        <v>6124.350640205982</v>
+        <v>7344.9311776775412</v>
       </c>
       <c r="L3">
-        <v>7874.1651088362623</v>
+        <v>9443.4829427282675</v>
       </c>
       <c r="M3">
-        <v>9623.9795774665436</v>
+        <v>11542.034707778994</v>
       </c>
       <c r="N3">
-        <v>1749.8144686302805</v>
+        <v>2098.5517650507263</v>
       </c>
       <c r="O3">
-        <v>3499.6289372605611</v>
+        <v>4197.1035301014526</v>
       </c>
       <c r="P3">
-        <v>5249.4434058908419</v>
+        <v>6295.655295152179</v>
       </c>
       <c r="Q3">
-        <v>6999.2578745211222</v>
+        <v>8394.2070602029053</v>
       </c>
       <c r="R3">
-        <v>8749.0723431514016</v>
+        <v>10492.75882525363</v>
       </c>
       <c r="S3">
-        <v>10498.886811781684</v>
+        <v>12591.310590304358</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -602,58 +602,58 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>269.62594073964215</v>
+        <v>286.34828714275784</v>
       </c>
       <c r="C4">
-        <v>1689.838886233556</v>
+        <v>1794.6436062227926</v>
       </c>
       <c r="D4">
-        <v>4732.0737877973852</v>
+        <v>5025.5595587420394</v>
       </c>
       <c r="E4">
-        <v>9279.9257115012842</v>
+        <v>9855.4717139267414</v>
       </c>
       <c r="F4">
-        <v>15334.087890803985</v>
+        <v>16285.116299948986</v>
       </c>
       <c r="G4">
-        <v>22900.586525397895</v>
+        <v>24320.893264659364</v>
       </c>
       <c r="H4">
-        <v>862.39866864964654</v>
+        <v>1034.2773510498653</v>
       </c>
       <c r="I4">
-        <v>2587.1960059489393</v>
+        <v>3102.8320531495956</v>
       </c>
       <c r="J4">
-        <v>4311.9933432482321</v>
+        <v>5171.3867552493257</v>
       </c>
       <c r="K4">
-        <v>6036.7906805475259</v>
+        <v>7239.9414573490567</v>
       </c>
       <c r="L4">
-        <v>7761.5880178468187</v>
+        <v>9308.4961594487868</v>
       </c>
       <c r="M4">
-        <v>9486.3853551461125</v>
+        <v>11377.050861548518</v>
       </c>
       <c r="N4">
-        <v>1724.7973372992931</v>
+        <v>2068.5547020997305</v>
       </c>
       <c r="O4">
-        <v>3449.5946745985862</v>
+        <v>4137.1094041994611</v>
       </c>
       <c r="P4">
-        <v>5174.3920118978785</v>
+        <v>6205.6641062991912</v>
       </c>
       <c r="Q4">
-        <v>6899.1893491971723</v>
+        <v>8274.2188083989222</v>
       </c>
       <c r="R4">
-        <v>8623.9866864964642</v>
+        <v>10342.773510498651</v>
       </c>
       <c r="S4">
-        <v>10348.784023795757</v>
+        <v>12411.328212598382</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -661,58 +661,58 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>320.09866081382995</v>
+        <v>342.72948159733147</v>
       </c>
       <c r="C5">
-        <v>2006.1688537484492</v>
+        <v>2148.0040231777566</v>
       </c>
       <c r="D5">
-        <v>5617.8959568613382</v>
+        <v>6015.0784888246026</v>
       </c>
       <c r="E5">
-        <v>11017.084574854662</v>
+        <v>11795.987135509933</v>
       </c>
       <c r="F5">
-        <v>18204.557711261252</v>
+        <v>19491.611152719026</v>
       </c>
       <c r="G5">
-        <v>27187.469642283329</v>
+        <v>29109.610620527688</v>
       </c>
       <c r="H5">
-        <v>811.28986513210236</v>
+        <v>972.98171761390756</v>
       </c>
       <c r="I5">
-        <v>2433.8695953963065</v>
+        <v>2918.9451528417221</v>
       </c>
       <c r="J5">
-        <v>4056.449325660511</v>
+        <v>4864.9085880695366</v>
       </c>
       <c r="K5">
-        <v>5679.029055924716</v>
+        <v>6810.8720232973519</v>
       </c>
       <c r="L5">
-        <v>7301.6087861889209</v>
+        <v>8756.8354585251673</v>
       </c>
       <c r="M5">
-        <v>8924.188516453125</v>
+        <v>10702.798893752983</v>
       </c>
       <c r="N5">
-        <v>1622.5797302642047</v>
+        <v>1945.9634352278151</v>
       </c>
       <c r="O5">
-        <v>3245.1594605284095</v>
+        <v>3891.9268704556303</v>
       </c>
       <c r="P5">
-        <v>4867.739190792613</v>
+        <v>5837.8903056834442</v>
       </c>
       <c r="Q5">
-        <v>6490.3189210568189</v>
+        <v>7783.8537409112605</v>
       </c>
       <c r="R5">
-        <v>8112.898651321022</v>
+        <v>9729.8171761390731</v>
       </c>
       <c r="S5">
-        <v>9735.4783815852261</v>
+        <v>11675.780611366889</v>
       </c>
     </row>
   </sheetData>

--- a/src/nodes/LPC/compressor_blade_self_frequency.xlsx
+++ b/src/nodes/LPC/compressor_blade_self_frequency.xlsx
@@ -722,9 +722,381 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor2</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor3</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor4</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor5</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor6</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage3</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage4</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage5</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>152.05526270493061</v>
+      </c>
+      <c r="C3">
+        <v>952.98284382572547</v>
+      </c>
+      <c r="D3">
+        <v>2668.6479830865051</v>
+      </c>
+      <c r="E3">
+        <v>5233.4042417199234</v>
+      </c>
+      <c r="F3">
+        <v>8647.6425679982221</v>
+      </c>
+      <c r="G3">
+        <v>12914.761430832912</v>
+      </c>
+      <c r="H3">
+        <v>519.78451907992053</v>
+      </c>
+      <c r="I3">
+        <v>1559.3535572397616</v>
+      </c>
+      <c r="J3">
+        <v>2598.9225953996024</v>
+      </c>
+      <c r="K3">
+        <v>3638.4916335594435</v>
+      </c>
+      <c r="L3">
+        <v>4678.060671719285</v>
+      </c>
+      <c r="M3">
+        <v>5717.6297098791256</v>
+      </c>
+      <c r="N3">
+        <v>1039.5690381598411</v>
+      </c>
+      <c r="O3">
+        <v>2079.1380763196821</v>
+      </c>
+      <c r="P3">
+        <v>3118.7071144795232</v>
+      </c>
+      <c r="Q3">
+        <v>4158.2761526393642</v>
+      </c>
+      <c r="R3">
+        <v>5197.8451907992048</v>
+      </c>
+      <c r="S3">
+        <v>6237.4142289590463</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>228.06177892662055</v>
+      </c>
+      <c r="C4">
+        <v>1429.3419299218851</v>
+      </c>
+      <c r="D4">
+        <v>4002.6013932361643</v>
+      </c>
+      <c r="E4">
+        <v>7849.3796267011094</v>
+      </c>
+      <c r="F4">
+        <v>12970.262998436108</v>
+      </c>
+      <c r="G4">
+        <v>19370.348739880566</v>
+      </c>
+      <c r="H4">
+        <v>525.2571832967709</v>
+      </c>
+      <c r="I4">
+        <v>1575.7715498903128</v>
+      </c>
+      <c r="J4">
+        <v>2626.2859164838542</v>
+      </c>
+      <c r="K4">
+        <v>3676.8002830773967</v>
+      </c>
+      <c r="L4">
+        <v>4727.3146496709387</v>
+      </c>
+      <c r="M4">
+        <v>5777.82901626448</v>
+      </c>
+      <c r="N4">
+        <v>1050.5143665935418</v>
+      </c>
+      <c r="O4">
+        <v>2101.0287331870836</v>
+      </c>
+      <c r="P4">
+        <v>3151.5430997806257</v>
+      </c>
+      <c r="Q4">
+        <v>4202.0574663741672</v>
+      </c>
+      <c r="R4">
+        <v>5252.5718329677084</v>
+      </c>
+      <c r="S4">
+        <v>6303.0861995612513</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>220.56702553508018</v>
+      </c>
+      <c r="C5">
+        <v>1382.3697220956906</v>
+      </c>
+      <c r="D5">
+        <v>3871.0646205768885</v>
+      </c>
+      <c r="E5">
+        <v>7591.4268699718259</v>
+      </c>
+      <c r="F5">
+        <v>12544.023568689416</v>
+      </c>
+      <c r="G5">
+        <v>18733.784438765255</v>
+      </c>
+      <c r="H5">
+        <v>506.29114303980555</v>
+      </c>
+      <c r="I5">
+        <v>1518.8734291194166</v>
+      </c>
+      <c r="J5">
+        <v>2531.455715199028</v>
+      </c>
+      <c r="K5">
+        <v>3544.0380012786391</v>
+      </c>
+      <c r="L5">
+        <v>4556.6202873582506</v>
+      </c>
+      <c r="M5">
+        <v>5569.2025734378622</v>
+      </c>
+      <c r="N5">
+        <v>1012.5822860796111</v>
+      </c>
+      <c r="O5">
+        <v>2025.1645721592222</v>
+      </c>
+      <c r="P5">
+        <v>3037.7468582388333</v>
+      </c>
+      <c r="Q5">
+        <v>4050.3291443184444</v>
+      </c>
+      <c r="R5">
+        <v>5062.9114303980559</v>
+      </c>
+      <c r="S5">
+        <v>6075.4937164776666</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
